--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse-list.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Liste contenant soit un événement de naissance, soit une observation sur la grossesse, mais pas les deux.</t>
+    <t>FrHistoriqueGrossesseList est une liste contenant soit un événement de naissance, soit une observation sur la grossesse, mais pas les deux.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -467,7 +467,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
